--- a/output/pdf_financials_xlsx/UNO.H.xlsx
+++ b/output/pdf_financials_xlsx/UNO.H.xlsx
@@ -1108,28 +1108,28 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.641002</v>
+        <v>-0.641002</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>3.850179</v>
+        <v>-3.850179</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>4.089235</v>
+        <v>-4.089235</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.084879</v>
+        <v>-0.084879</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.122729</v>
+        <v>-0.122729</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1.328118</v>
+        <v>-1.328118</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.075707</v>
+        <v>-0.075707</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.063425</v>
+        <v>-0.063425</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>-0.053493</v>
@@ -1346,28 +1346,28 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.641002</v>
+        <v>-0.641002</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>3.850179</v>
+        <v>-3.850179</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>4.089235</v>
+        <v>-4.089235</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.084879</v>
+        <v>-0.084879</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.122729</v>
+        <v>-0.122729</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1.328118</v>
+        <v>-1.328118</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.075707</v>
+        <v>-0.075707</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.063425</v>
+        <v>-0.063425</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>-0.053493</v>
@@ -1486,28 +1486,28 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.641002</v>
+        <v>-0.641002</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>3.850179</v>
+        <v>-3.850179</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>4.089235</v>
+        <v>-4.089235</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.084879</v>
+        <v>-0.084879</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.122729</v>
+        <v>-0.122729</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1.328118</v>
+        <v>-1.328118</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.075707</v>
+        <v>-0.075707</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.063425</v>
+        <v>-0.063425</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>-0.053493</v>
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>12.82004</v>
+        <v>-12.82004</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>42.779767</v>
+        <v>-42.779767</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>136.307833</v>
+        <v>-136.307833</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -1688,28 +1688,28 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.641002</v>
+        <v>-0.641002</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3.850179</v>
+        <v>-3.850179</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>4.089235</v>
+        <v>-4.089235</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.084879</v>
+        <v>-0.084879</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.122729</v>
+        <v>-0.122729</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.328118</v>
+        <v>-1.328118</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.075707</v>
+        <v>-0.075707</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.063425</v>
+        <v>-0.063425</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-0.053493</v>
@@ -1782,28 +1782,28 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.641002</v>
+        <v>-0.641002</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>3.850179</v>
+        <v>-3.850179</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>4.089235</v>
+        <v>-4.089235</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.084879</v>
+        <v>-0.084879</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.122729</v>
+        <v>-0.122729</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1.328118</v>
+        <v>-1.328118</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.075707</v>
+        <v>-0.075707</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.063425</v>
+        <v>-0.063425</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-0.053493</v>
@@ -1902,28 +1902,28 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>-0</v>
@@ -4769,31 +4769,31 @@
         <v>0.197911</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.197911</v>
+        <v>0.328536</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.055411</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.137511</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.563449</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.563449</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.5234490000000001</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.454141</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.454141</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.454141</v>
       </c>
       <c r="L92" s="3" t="n">
         <v>0</v>
@@ -9133,7 +9133,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -9617,7 +9621,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -10488,7 +10496,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -11800,7 +11812,11 @@
           <t>Reserves 7 1,055,411</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -13037,7 +13053,11 @@
           <t>Warrants reserve</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -24699,10 +24719,10 @@
         </is>
       </c>
       <c r="M222" s="5" t="n">
-        <v>0.063425</v>
+        <v>-0.063425</v>
       </c>
       <c r="N222" s="5" t="n">
-        <v>0.053493</v>
+        <v>-0.053493</v>
       </c>
       <c r="O222" t="inlineStr">
         <is>
@@ -25499,10 +25519,10 @@
         </is>
       </c>
       <c r="K232" s="5" t="n">
-        <v>1.328118</v>
+        <v>-1.328118</v>
       </c>
       <c r="L232" s="5" t="n">
-        <v>0.075707</v>
+        <v>-0.075707</v>
       </c>
       <c r="M232" t="inlineStr">
         <is>
@@ -26150,10 +26170,10 @@
         </is>
       </c>
       <c r="J240" s="5" t="n">
-        <v>0.122729</v>
+        <v>-0.122729</v>
       </c>
       <c r="K240" s="5" t="n">
-        <v>1.328118</v>
+        <v>-1.328118</v>
       </c>
       <c r="L240" t="inlineStr">
         <is>
@@ -26799,10 +26819,10 @@
         </is>
       </c>
       <c r="I248" s="5" t="n">
-        <v>0.084879</v>
+        <v>-0.084879</v>
       </c>
       <c r="J248" s="5" t="n">
-        <v>0.122729</v>
+        <v>-0.122729</v>
       </c>
       <c r="K248" t="inlineStr">
         <is>
@@ -27365,10 +27385,10 @@
         </is>
       </c>
       <c r="H255" s="5" t="n">
-        <v>4.089235</v>
+        <v>-4.089235</v>
       </c>
       <c r="I255" s="5" t="n">
-        <v>0.084879</v>
+        <v>-0.084879</v>
       </c>
       <c r="J255" t="inlineStr">
         <is>
@@ -28093,10 +28113,10 @@
         </is>
       </c>
       <c r="G264" s="5" t="n">
-        <v>3.850179</v>
+        <v>-3.850179</v>
       </c>
       <c r="H264" s="5" t="n">
-        <v>4.089235</v>
+        <v>-4.089235</v>
       </c>
       <c r="I264" t="inlineStr">
         <is>
@@ -28665,10 +28685,10 @@
         </is>
       </c>
       <c r="F271" s="5" t="n">
-        <v>0.641002</v>
+        <v>-0.641002</v>
       </c>
       <c r="G271" s="5" t="n">
-        <v>3.850179</v>
+        <v>-3.850179</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/UNO.H.xlsx
+++ b/output/pdf_financials_xlsx/UNO.H.xlsx
@@ -925,13 +925,13 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001733</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004568</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000958</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1691,13 +1691,13 @@
         <v>-0.641002</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.850179</v>
+        <v>-3.848446</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-4.089235</v>
+        <v>-4.084667</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.084879</v>
+        <v>-0.083921</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.122729</v>
@@ -1785,13 +1785,13 @@
         <v>-0.641002</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.850179</v>
+        <v>-3.848446</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4.089235</v>
+        <v>-4.084667</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.084879</v>
+        <v>-0.083921</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.122729</v>
@@ -2024,43 +2024,43 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.015948</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.013322</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.7569129999999999</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.270591</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.124799</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.004548</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.013241</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.00046</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.007434</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.001228</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.000199</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.01016</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.117848</v>
       </c>
     </row>
     <row r="35">
@@ -2116,43 +2116,43 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.015948</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.013322</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.7569129999999999</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.270591</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.124799</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.004548</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.013241</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.00046</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.007434</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.001228</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.000199</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.01016</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.117848</v>
       </c>
     </row>
     <row r="37">
@@ -2668,43 +2668,43 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.027948</v>
+        <v>0.012</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.032743</v>
+        <v>0.019421</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.830954</v>
+        <v>0.074041</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.344632</v>
+        <v>0.074041</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.19884</v>
+        <v>0.074041</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.107073</v>
+        <v>0.102525</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.019074</v>
+        <v>0.005833</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.006293</v>
+        <v>0.005833</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.010934</v>
+        <v>0.0035</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.005166</v>
+        <v>0.003938</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.000199</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.01016</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.167848</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="49">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -12227,7 +12227,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
@@ -21236,7 +21236,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -23077,7 +23077,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -27204,7 +27204,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -27937,7 +27937,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">

--- a/output/pdf_financials_xlsx/UNO.H.xlsx
+++ b/output/pdf_financials_xlsx/UNO.H.xlsx
@@ -3579,40 +3579,40 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.09159399999999999</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.04384</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.01005</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.0075</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.008081</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.025285</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.0175</v>
       </c>
     </row>
     <row r="68">
